--- a/data/sources/countries/panama.xlsx
+++ b/data/sources/countries/panama.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI56"/>
+  <dimension ref="A1:BE56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -827,7 +731,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -865,12 +769,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Compra de espacio de oficina</t>
+          <t>Compra De Espacio De Oficina</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Purchase of office space</t>
+          <t>Purchase Of Office Space</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -899,25 +803,20 @@
       <c r="BA2" t="n">
         <v>3</v>
       </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>Huawei estableció su sede regional para América Latina en Panamá en 2011, y en 2015 construyó un Supply Center en la Zona Libre de Colón. Ha creado más de 300 empleos para panameños. Allison confirma que el monto no se puede confirmar. La presencia de Huawei en Panamá está bien documentada pero el monto específico de USD 58M para 'compra de oficina' en 2011 no se verifica en ninguna fuente. | Fuentes adicionales: http://en.yibada.com/articles/70229/20151003/huawei-latin-america-distribution-center-panama.htm</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>http://www.china.org.cn/world/Off_the_Wire/2015-10/02/content_36731925.htm</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>https://americasquarterly.org/article/u-s-pressure-on-huawei-reaches-new-heights-in-panama/</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
-        <is>
-          <t>http://www.china.org.cn/world/Off_the_Wire/2015-10/02/content_36731925.htm</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>https://americasquarterly.org/article/u-s-pressure-on-huawei-reaches-new-heights-in-panama/</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
         <is>
           <t>https://diazdiaz.com/article/huawei-latam-headquarters-integration-of-technology-and-design</t>
         </is>
@@ -950,7 +849,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -988,12 +887,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Centro de distribución</t>
+          <t>Centro De Distribución</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Distribution hub</t>
+          <t>Distribution Hub</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1022,15 +921,15 @@
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>https://www.prnewswire.com/news-releases/renesola-establishes-regional-sales-office-in-panama-244849231.html</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>https://www.solarpowerworldonline.com/2014/02/renesola-establishes-regional-sales-office-panama/</t>
         </is>
@@ -1063,7 +962,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -1101,12 +1000,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Construcción del Centro de Convenciones Amador en joint venture con CCA</t>
+          <t>Construcción Del Centro De Convenciones Amador En Joint Venture Con Cca</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Construction of the Amador Convention Center in joint venture with CCA</t>
+          <t>Construction Of The Amador Convention Center In Joint Venture With Cca</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1155,25 +1054,20 @@
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>Bien documentado: el consorcio CCA-COCIGE (China Construction America + CSCEC + Construcciones Civiles Generales) retomó la construcción del Centro de Convenciones de Amador en febrero 2016 por USD 193M. El monto registrado es USD 207M (posiblemente incluye ajustes). Inaugurado en mayo 2019. Confirmado por CCA, CentralAmericaData y medios internacionales.</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>https://www.chinaconstruction.us/project/amador-convention-center/</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>https://centralamericadata.com/en/article/home/Panama_New_Contractor_for_Convention_Center</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
-        <is>
-          <t>https://www.chinaconstruction.us/project/amador-convention-center/</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>https://centralamericadata.com/en/article/home/Panama_New_Contractor_for_Convention_Center</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
         <is>
           <t>https://www.alwihdainfo.com/Chinese-company-builds-Panama-s-largest-convention-center-enhances-bilateral-ties_a68859.html</t>
         </is>
@@ -1206,7 +1100,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -1244,12 +1138,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Construcción de un puerto de cruceros en joint venture con Jan de Nul</t>
+          <t>Construcción De Un Puerto De Cruceros En Joint Venture Con Jan De Nul</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Construction of cruise port in joint venture with Jan de Nul</t>
+          <t>Construction Of Cruise Port In Joint Venture With Jan De Nul</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1298,25 +1192,20 @@
       <c r="BA5" t="n">
         <v>5</v>
       </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>Muy bien documentado: CHEC y Jan de Nul ganaron contrato en julio 2017 por USD 165.7M para construir la terminal de cruceros de Fuerte Amador. Ceremonia de inicio el 18 de octubre de 2017. Confirmado por múltiples fuentes especializadas: Maritime Executive, Seatrade Cruise, Chronicle.lu.</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>https://maritime-executive.com/article/chec-starts-construction-on-panama-city-cruise-terminal</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>https://chronicle.lu/category/transport-logistics/23694-jan-de-nul-help-construct-amador-cruise-port-in-panama</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
-        <is>
-          <t>https://maritime-executive.com/article/chec-starts-construction-on-panama-city-cruise-terminal</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>https://chronicle.lu/category/transport-logistics/23694-jan-de-nul-help-construct-amador-cruise-port-in-panama</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
         <is>
           <t>https://www.seatrade-cruise.com/news-headlines/belgium-china-consortium-wins-166m-panama-cruise-terminal-contract</t>
         </is>
@@ -1349,7 +1238,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -1387,12 +1276,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Centro de distribución</t>
+          <t>Centro De Distribución</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Distribution hub</t>
+          <t>Distribution Hub</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1421,25 +1310,20 @@
       <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>Bien documentado: Huawei inauguró centro de distribución latinoamericano en la Zona Libre de Colón el 1 de octubre de 2015, con 10,000 m² de instalaciones. El monto de USD 40M es plausible. Confirmado por China.org.cn y Global Times. El Presidente de Panamá asistió a la inauguración.</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>http://www.china.org.cn/world/Off_the_Wire/2015-10/02/content_36731925.htm</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>https://www.globaltimes.cn/content/945380.shtml</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
-        <is>
-          <t>http://www.china.org.cn/world/Off_the_Wire/2015-10/02/content_36731925.htm</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>https://www.globaltimes.cn/content/945380.shtml</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
         <is>
           <t>https://www.tropicalrealtypanama.com/en/huawei-panama/</t>
         </is>
@@ -1472,7 +1356,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -1510,12 +1394,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Construcción de la ampliación del Anillo Hidráulico a Panamá Este</t>
+          <t>Construcción De La Ampliación Del Anillo Hidráulico A Panamá Este</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Construction of Hydraulic Ring extension to Panama East</t>
+          <t>Construction Of Hydraulic Ring Extension To Panama East</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1544,15 +1428,15 @@
       <c r="BA7" t="n">
         <v>3</v>
       </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="inlineStr">
         <is>
           <t>https://thebusinessyear.com/interview/significant-player/</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>https://www.panamaamerica.com.pa/nacion/pagos-empresas-que-construyen-anillos-hidraulicos-estan-al-dia-1236071</t>
         </is>
@@ -1585,7 +1469,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -1623,12 +1507,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Construcción del cuarto puente sobre el Canal de Panamá</t>
+          <t>Construcción Del Cuarto Puente Sobre El Canal De Panamá</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Construction of fourth bridge over the Panama Canal</t>
+          <t>Construction Of Fourth Bridge Over The Panama Canal</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1667,25 +1551,20 @@
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>Ampliamente documentado: China Daily, Diálogo Américas, CHEC Americas oficial. CCCC/CHEC ganó contrato cuarto puente sobre el Canal de Panamá por $1.4B. Adjudicado jul 2018, orden de proceder dic 2018. Datos coinciden con la base.</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
-        <is>
-          <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
         <is>
           <t>https://www.checamerica.com/projects-fourth-bridge/</t>
         </is>
@@ -1718,7 +1597,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -1756,12 +1635,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Construcción del cuarto puente sobre el Canal de Panamá</t>
+          <t>Construcción Del Cuarto Puente Sobre El Canal De Panamá</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Construction of fourth bridge over the Panama Canal</t>
+          <t>Construction Of Fourth Bridge Over The Panama Canal</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1800,25 +1679,20 @@
       <c r="BA9" t="n">
         <v>5</v>
       </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>Ampliamente documentado: China Daily, Diálogo Américas, CHEC Americas oficial. CCCC/CHEC ganó contrato cuarto puente sobre el Canal de Panamá por $1.4B. Adjudicado jul 2018, orden de proceder dic 2018. Datos coinciden con la base.</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
-        <is>
-          <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
         <is>
           <t>https://www.checamerica.com/projects-fourth-bridge/</t>
         </is>
@@ -1851,7 +1725,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -1889,12 +1763,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Construcción del cuarto puente sobre el Canal de Panamá</t>
+          <t>Construcción Del Cuarto Puente Sobre El Canal De Panamá</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Construction of fourth bridge over the Panama Canal</t>
+          <t>Construction Of Fourth Bridge Over The Panama Canal</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1933,25 +1807,20 @@
       <c r="BA10" t="n">
         <v>5</v>
       </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>Ampliamente documentado: China Daily, Diálogo Américas, CHEC Americas oficial. CCCC/CHEC ganó contrato cuarto puente sobre el Canal de Panamá por $1.4B. Adjudicado jul 2018, orden de proceder dic 2018. Datos coinciden con la base.</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
-        <is>
-          <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
         <is>
           <t>https://www.checamerica.com/projects-fourth-bridge/</t>
         </is>
@@ -1984,7 +1853,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -2022,12 +1891,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Construcción del cuarto puente sobre el Canal de Panamá</t>
+          <t>Construcción Del Cuarto Puente Sobre El Canal De Panamá</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Construction of fourth bridge over the Panama Canal</t>
+          <t>Construction Of Fourth Bridge Over The Panama Canal</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2066,25 +1935,20 @@
       <c r="BA11" t="n">
         <v>5</v>
       </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>Ampliamente documentado: China Daily, Diálogo Américas, CHEC Americas oficial. CCCC/CHEC ganó contrato cuarto puente sobre el Canal de Panamá por $1.4B. Adjudicado jul 2018, orden de proceder dic 2018. Datos coinciden con la base.</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
-        <is>
-          <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
         <is>
           <t>https://www.checamerica.com/projects-fourth-bridge/</t>
         </is>
@@ -2117,7 +1981,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -2155,12 +2019,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Compra de espacio de oficina</t>
+          <t>Compra De Espacio De Oficina</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Purchase of office space</t>
+          <t>Purchase Of Office Space</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2189,25 +2053,15 @@
       <c r="BA12" t="n">
         <v>1</v>
       </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>Allison dice: 'Eliminar entrada. No existe la compra de oficinas por CCA'. Sin embargo, CCA sí abrió oficina regional en Panamá en abril 2015 (Oceania Business Plaza, Torre 1000, piso 52). La apertura fue un evento con \~300 invitados y fue reportada por múltiples medios. El tema es que fue apertura de oficina (posiblemente arrendada), no compra de USD 5M. La presencia existe pero la descripción como 'compra' es cuestionable.</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>1</v>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>https://www.chinaconstruction.us/</t>
+        </is>
       </c>
       <c r="BD12" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>https://www.chinaconstruction.us/</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
         <is>
           <t>https://www.chinaconstruction.us/news/grand-opening-cca-expanded-to-latin-america/</t>
         </is>
@@ -2240,7 +2094,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -2278,12 +2132,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Construcción del proyecto fotovoltaico</t>
+          <t>Construcción Del Proyecto Fotovoltaico</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Construction of photovoltaic project</t>
+          <t>Construction Of Photovoltaic Project</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2312,25 +2166,20 @@
       <c r="BA13" t="n">
         <v>4</v>
       </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>Contrato EPC confirmado por comunicado oficial de CGGC en MarketScreener y por Seetao, con monto de USD 108M (no 110M). El proyecto Panasolar está documentado de forma independiente. Diferencia menor entre el monto registrado (USD 110M) y el monto contractual (USD 108M).</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/news/latest/CGGC-China-Gezhouba-Signs-An-EPC-Contract-Agreement-for-the-Panamanian-110MW-PV-Project--30671118/</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>https://www.seetao.com/details/25785.html</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/news/latest/CGGC-China-Gezhouba-Signs-An-EPC-Contract-Agreement-for-the-Panamanian-110MW-PV-Project--30671118/</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>https://www.seetao.com/details/25785.html</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
         <is>
           <t>https://www.power-technology.com/marketdata/power-plant-profile-panasolar-solar-pv-park-panama/</t>
         </is>
@@ -2363,7 +2212,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -2401,12 +2250,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Construcción del tercer puente sobre el Canal de Panamá</t>
+          <t>Construcción Del Tercer Puente Sobre El Canal De Panamá</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Construction of third bridge over the Panama Canal</t>
+          <t>Construction Of Third Bridge Over The Panama Canal</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2435,15 +2284,10 @@
       <c r="BA14" t="n">
         <v>0</v>
       </c>
-      <c r="BC14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Third_Bridge_over_Panama_Canal</t>
         </is>
@@ -2476,7 +2320,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -2514,12 +2358,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Construcción del tercer puente sobre el Canal de Panamá</t>
+          <t>Construcción Del Tercer Puente Sobre El Canal De Panamá</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Construction of third bridge over the Panama Canal</t>
+          <t>Construction Of Third Bridge Over The Panama Canal</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2548,15 +2392,10 @@
       <c r="BA15" t="n">
         <v>0</v>
       </c>
-      <c r="BC15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Third_Bridge_over_Panama_Canal</t>
         </is>
@@ -2589,7 +2428,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -2627,12 +2466,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Construcción del tercer puente sobre el Canal de Panamá</t>
+          <t>Construcción Del Tercer Puente Sobre El Canal De Panamá</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Construction of third bridge over the Panama Canal</t>
+          <t>Construction Of Third Bridge Over The Panama Canal</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2661,15 +2500,10 @@
       <c r="BA16" t="n">
         <v>0</v>
       </c>
-      <c r="BC16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Third_Bridge_over_Panama_Canal</t>
         </is>
@@ -2702,7 +2536,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -2740,12 +2574,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Construcción de proyecto de desarrollo residencial en Ciudad de Esperanza</t>
+          <t>Construcción De Proyecto De Desarrollo Residencial En Ciudad De Esperanza</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Construction of residential development project in Ciudad de Esperanza</t>
+          <t>Construction Of Residential Development Project In Ciudad De Esperanza</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2774,25 +2608,20 @@
       <c r="BA17" t="n">
         <v>5</v>
       </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>Muy bien documentado: CCA-MCM Consortium inició construcción de Ciudad de Esperanza (City of Hope) en Arraiján el 19 de octubre de 2015 por USD 137M. 2,250 viviendas para 11,250 personas. Confirmado por CCA, Global Construction Review y Global Times. Monto y detalles consistentes con la entrada.</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>https://www.chinaconstruction.us/project/city-of-hope/</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>https://www.globalconstructionreview.com/chinese-contract8or-beg3ins-work-137m-tow8n-panama/</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
-        <is>
-          <t>https://www.chinaconstruction.us/project/city-of-hope/</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>https://www.globalconstructionreview.com/chinese-contract8or-beg3ins-work-137m-tow8n-panama/</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/content/948056.shtml</t>
         </is>
@@ -2825,7 +2654,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -2863,12 +2692,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Construcción de estación de autobus de San Isidro</t>
+          <t>Construcción De Estación De Autobus De San Isidro</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Construction of San Isidro bus station</t>
+          <t>Construction Of San Isidro Bus Station</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2897,20 +2726,15 @@
       <c r="BA18" t="n">
         <v>3</v>
       </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>Confirmado: China Construction America (filial de CSCEC) construyó la estación de buses San Isidro en San Miguelito, primer proyecto de infraestructura de CCA en Panamá. Contrato de \~USD 30M con período de construcción de 540 días. Confirmado por CCA y Chinascope.</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="inlineStr">
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="inlineStr">
         <is>
           <t>https://www.chinaconstruction.us/project/san-isidro-bus-station/</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BD18" t="inlineStr">
         <is>
           <t>https://chinascope.org/archives/16937</t>
         </is>
@@ -2943,7 +2767,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -2981,12 +2805,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sucursal de ICBC Panamá</t>
+          <t>Sucursal De Icbc Panamá</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>ICBC Panama headquarters</t>
+          <t>Icbc Panama Headquarters</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3001,7 +2825,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3022,25 +2846,20 @@
       <c r="BA19" t="n">
         <v>3</v>
       </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>ICBC obtuvo licencia bancaria general en Panamá el 12 de junio de 2020, convirtiéndose en el primer banco chino en el país. La licencia fue otorgada por la Superintendencia de Bancos de Panamá. Allison confirma que no puede verificar el monto de USD 3M. El monto estimado parece corresponder a costos de establecimiento de la sucursal. | Fuentes adicionales: https://www.newsroompanama.com/business/giant-china-bank-granted-panama-license</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>https://www.icbc.com.cn/icbc/en/newsupdates/icbc%20news/ICBCPanamaBranchIsGrantedLicense.htm</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>https://www.panamabanks.info/banks/industrial-and-commercial-bank-of-china-limited</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
-        <is>
-          <t>https://www.icbc.com.cn/icbc/en/newsupdates/icbc%20news/ICBCPanamaBranchIsGrantedLicense.htm</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>https://www.panamabanks.info/banks/industrial-and-commercial-bank-of-china-limited</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
         <is>
           <t>https://www.designbycpu.com/projects/icbcpanama</t>
         </is>
@@ -3073,7 +2892,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -3111,12 +2930,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3145,25 +2964,20 @@
       <c r="BA20" t="n">
         <v>3</v>
       </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3196,7 +3010,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -3234,12 +3048,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3268,25 +3082,20 @@
       <c r="BA21" t="n">
         <v>3</v>
       </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3319,7 +3128,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -3357,12 +3166,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3391,25 +3200,20 @@
       <c r="BA22" t="n">
         <v>3</v>
       </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3442,7 +3246,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -3480,12 +3284,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3514,25 +3318,20 @@
       <c r="BA23" t="n">
         <v>3</v>
       </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3565,7 +3364,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -3603,12 +3402,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3637,25 +3436,20 @@
       <c r="BA24" t="n">
         <v>3</v>
       </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC24" t="n">
-        <v>0</v>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF24" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG24" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3688,7 +3482,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -3726,12 +3520,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3760,25 +3554,20 @@
       <c r="BA25" t="n">
         <v>3</v>
       </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3811,7 +3600,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -3849,12 +3638,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3883,25 +3672,20 @@
       <c r="BA26" t="n">
         <v>3</v>
       </c>
-      <c r="BB26" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3934,7 +3718,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -3972,12 +3756,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4006,25 +3790,20 @@
       <c r="BA27" t="n">
         <v>3</v>
       </c>
-      <c r="BB27" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF27" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG27" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4057,7 +3836,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -4095,12 +3874,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4129,25 +3908,20 @@
       <c r="BA28" t="n">
         <v>3</v>
       </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF28" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4180,7 +3954,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -4218,12 +3992,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4252,25 +4026,20 @@
       <c r="BA29" t="n">
         <v>3</v>
       </c>
-      <c r="BB29" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4303,7 +4072,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -4341,12 +4110,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4375,25 +4144,20 @@
       <c r="BA30" t="n">
         <v>3</v>
       </c>
-      <c r="BB30" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF30" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4426,7 +4190,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -4464,12 +4228,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4498,25 +4262,20 @@
       <c r="BA31" t="n">
         <v>3</v>
       </c>
-      <c r="BB31" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4549,7 +4308,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -4587,12 +4346,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4621,25 +4380,20 @@
       <c r="BA32" t="n">
         <v>3</v>
       </c>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4672,7 +4426,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -4710,12 +4464,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4744,25 +4498,20 @@
       <c r="BA33" t="n">
         <v>3</v>
       </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4795,7 +4544,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -4833,12 +4582,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4867,25 +4616,20 @@
       <c r="BA34" t="n">
         <v>3</v>
       </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4918,7 +4662,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -4956,12 +4700,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4990,25 +4734,20 @@
       <c r="BA35" t="n">
         <v>3</v>
       </c>
-      <c r="BB35" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC35" t="n">
-        <v>0</v>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5041,7 +4780,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -5079,12 +4818,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -5113,25 +4852,20 @@
       <c r="BA36" t="n">
         <v>3</v>
       </c>
-      <c r="BB36" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF36" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5164,7 +4898,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -5202,12 +4936,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -5236,25 +4970,20 @@
       <c r="BA37" t="n">
         <v>3</v>
       </c>
-      <c r="BB37" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC37" t="n">
-        <v>0</v>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5287,7 +5016,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -5325,12 +5054,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5359,25 +5088,20 @@
       <c r="BA38" t="n">
         <v>3</v>
       </c>
-      <c r="BB38" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC38" t="n">
-        <v>0</v>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF38" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG38" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5410,7 +5134,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -5448,12 +5172,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -5482,25 +5206,20 @@
       <c r="BA39" t="n">
         <v>3</v>
       </c>
-      <c r="BB39" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC39" t="n">
-        <v>0</v>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF39" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG39" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5533,7 +5252,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -5571,12 +5290,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5605,25 +5324,20 @@
       <c r="BA40" t="n">
         <v>3</v>
       </c>
-      <c r="BB40" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF40" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG40" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5656,7 +5370,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -5694,12 +5408,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -5728,25 +5442,20 @@
       <c r="BA41" t="n">
         <v>3</v>
       </c>
-      <c r="BB41" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC41" t="n">
-        <v>0</v>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF41" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG41" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5779,7 +5488,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -5817,12 +5526,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -5851,25 +5560,20 @@
       <c r="BA42" t="n">
         <v>3</v>
       </c>
-      <c r="BB42" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC42" t="n">
-        <v>0</v>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF42" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG42" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5902,7 +5606,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -5940,12 +5644,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -5974,25 +5678,20 @@
       <c r="BA43" t="n">
         <v>3</v>
       </c>
-      <c r="BB43" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC43" t="n">
-        <v>0</v>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG43" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -6025,7 +5724,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -6063,12 +5762,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6097,25 +5796,20 @@
       <c r="BA44" t="n">
         <v>3</v>
       </c>
-      <c r="BB44" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC44" t="n">
-        <v>0</v>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF44" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -6148,7 +5842,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -6186,12 +5880,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6220,25 +5914,20 @@
       <c r="BA45" t="n">
         <v>3</v>
       </c>
-      <c r="BB45" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC45" t="n">
-        <v>0</v>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF45" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG45" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -6271,7 +5960,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -6309,12 +5998,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -6343,25 +6032,20 @@
       <c r="BA46" t="n">
         <v>3</v>
       </c>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC46" t="n">
-        <v>0</v>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG46" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -6394,7 +6078,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -6432,12 +6116,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -6466,25 +6150,20 @@
       <c r="BA47" t="n">
         <v>3</v>
       </c>
-      <c r="BB47" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC47" t="n">
-        <v>0</v>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF47" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG47" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -6517,7 +6196,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -6555,12 +6234,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Construccion del túnel de la Línea 3 del Metro</t>
+          <t>Construccion Del Túnel De La Línea 3 Del Metro</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Construction of Metro Line 3 tunnel</t>
+          <t>Construction Of Metro Line 3 Tunnel</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -6589,25 +6268,20 @@
       <c r="BA48" t="n">
         <v>3</v>
       </c>
-      <c r="BB48" t="inlineStr">
-        <is>
-          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
-        </is>
-      </c>
-      <c r="BC48" t="n">
-        <v>0</v>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
+        </is>
+      </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
-        <is>
-          <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
-        </is>
-      </c>
-      <c r="BF48" t="inlineStr">
-        <is>
-          <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
-        </is>
-      </c>
-      <c r="BG48" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -6640,7 +6314,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -6678,12 +6352,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Construcción de proyecto de viviendas "Ciudad de Esperanza"</t>
+          <t>Construcción De Proyecto De Viviendas "Ciudad De Esperanza"</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Construction of "Ciudad de Esperanza" housing project</t>
+          <t>Construction Of "Ciudad De Esperanza" Housing Project</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -6712,25 +6386,20 @@
       <c r="BA49" t="n">
         <v>4</v>
       </c>
-      <c r="BB49" t="inlineStr">
-        <is>
-          <t>Confirmado por sitio oficial CCA, Global Construction Review, Global Times. China Construction America construyó 'Ciudad de Esperanza' en Vacamonte/Arraiján por $137-156M (2,130-2,250 apartamentos). Adjudicado 2015, entrega programada 2018. Base registra $156M.</t>
-        </is>
-      </c>
-      <c r="BC49" t="n">
-        <v>0</v>
+      <c r="BB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>https://www.chinaconstruction.us/project/city-of-hope/</t>
+        </is>
+      </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>https://www.globalconstructionreview.com/chinese-contract8or-beg3ins-work-137m-tow8n-panama/</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
-        <is>
-          <t>https://www.chinaconstruction.us/project/city-of-hope/</t>
-        </is>
-      </c>
-      <c r="BF49" t="inlineStr">
-        <is>
-          <t>https://www.globalconstructionreview.com/chinese-contract8or-beg3ins-work-137m-tow8n-panama/</t>
-        </is>
-      </c>
-      <c r="BG49" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/content/948056.shtml</t>
         </is>
@@ -6763,7 +6432,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -6801,12 +6470,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Proyecto de modernización de la Aduana de Panamá</t>
+          <t>Proyecto De Modernización De La Aduana De Panamá</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Panama Customs modernization project</t>
+          <t>Panama Customs Modernization Project</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -6835,20 +6504,15 @@
       <c r="BA50" t="n">
         <v>2</v>
       </c>
-      <c r="BC50" t="n">
-        <v>1</v>
+      <c r="BB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>https://www.aiddata.org/blog/chinas-global-scanner-dissemination</t>
+        </is>
       </c>
       <c r="BD50" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE50" t="inlineStr">
-        <is>
-          <t>https://www.aiddata.org/blog/chinas-global-scanner-dissemination</t>
-        </is>
-      </c>
-      <c r="BF50" t="inlineStr">
         <is>
           <t>https://www.importgenius.com/panama/importers/nuctech-panama-s-a</t>
         </is>
@@ -6881,7 +6545,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -6919,12 +6583,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Construcción en proyecto del dragado del Puerto Balboa</t>
+          <t>Construcción En Proyecto Del Dragado Del Puerto Balboa</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Construction in dredging project in the Balboa port</t>
+          <t>Construction In Dredging Project In The Balboa Port</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -6950,30 +6614,20 @@
       <c r="BA51" t="n">
         <v>2</v>
       </c>
-      <c r="BB51" t="inlineStr">
-        <is>
-          <t>Allison confirma el proyecto y proporciona URL de CCCC en español como evidencia adicional. CCCC Shanghai Dredging tiene presencia registrada en Panamá (Volza, BNamericas). El proyecto de dragado en puerto Balboa en 2024 está confirmado por la propia CCCC. El monto figura como NA, lo cual es consistente con la dificultad de verificar el valor exacto del contrato.</t>
-        </is>
-      </c>
-      <c r="BC51" t="n">
-        <v>1</v>
+      <c r="BB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/company-profile/cccc-shanghai-dredging-co-ltd-sdc</t>
+        </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
+          <t>https://www.volza.com/company-profile/cccc-shanghai-dredging-company-ltd.-94452941/</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/company-profile/cccc-shanghai-dredging-co-ltd-sdc</t>
-        </is>
-      </c>
-      <c r="BF51" t="inlineStr">
-        <is>
-          <t>https://www.volza.com/company-profile/cccc-shanghai-dredging-company-ltd.-94452941/</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
         <is>
           <t>https://espanol.ccccltd.cn/xwzx/ztbd/202403/t20240311_213230.html</t>
         </is>
@@ -7006,7 +6660,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -7044,12 +6698,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Adquisición completa de la finca de café Carmen Estate</t>
+          <t>Adquisición Completa De La Finca De Café Carmen Estate</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Full acquisition of Carmen Estate coffee plantation</t>
+          <t>Full Acquisition Of Carmen Estate Coffee Plantation</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -7075,25 +6729,15 @@
       <c r="BA52" t="n">
         <v>1</v>
       </c>
-      <c r="BB52" t="inlineStr">
-        <is>
-          <t>Allison confirma que la operación existe pero no encuentra fecha ni monto. La búsqueda web confirma que Dashang Group (Dalian, China) adquirió Carmen Estate, pero la fecha registrada (2019) no coincide — las fuentes indican que la transferencia ocurrió en 2023. El monto de USD 10M\* no se puede verificar. La operación es real pero año y monto son dudosos.</t>
-        </is>
-      </c>
-      <c r="BC52" t="n">
-        <v>1</v>
+      <c r="BB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>https://www.roastmasters.com/carmen_copy.html</t>
+        </is>
       </c>
       <c r="BD52" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE52" t="inlineStr">
-        <is>
-          <t>https://www.roastmasters.com/carmen_copy.html</t>
-        </is>
-      </c>
-      <c r="BF52" t="inlineStr">
         <is>
           <t>https://www.chinadaily.com.cn/a/202311/06/WS6548e942a31090682a5ecb99.html</t>
         </is>
@@ -7126,7 +6770,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -7164,12 +6808,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Adquisición completa de Panama Cables &amp; Engineering Company</t>
+          <t>Adquisición Completa De Panama Cables &amp; Engineering Company</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Full acquisition of Panama Cables &amp; Engineering</t>
+          <t>Full Acquisition Of Panama Cables &amp; Engineering</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -7198,20 +6842,20 @@
       <c r="BA53" t="n">
         <v>3</v>
       </c>
-      <c r="BC53" t="n">
-        <v>0</v>
+      <c r="BB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>https://www.cbinsights.com/company/panama-cables-engineering</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>https://www.hebei-huatong.com/news/the-future-is-coming-from-the-past.html</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
-        <is>
-          <t>https://www.cbinsights.com/company/panama-cables-engineering</t>
-        </is>
-      </c>
-      <c r="BF53" t="inlineStr">
-        <is>
-          <t>https://www.hebei-huatong.com/news/the-future-is-coming-from-the-past.html</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr">
         <is>
           <t>https://www.hebei-huatong.com/en</t>
         </is>
@@ -7244,7 +6888,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -7282,12 +6926,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Compra de almacén en Colón Free Trade Zone</t>
+          <t xml:space="preserve">Compra De Almacén En Colón Free Trade Zone </t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Purchase of warehouse in Colón Free Trade Zone</t>
+          <t>Purchase Of Warehouse In Colón Free Trade Zone</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -7313,30 +6957,20 @@
       <c r="BA54" t="n">
         <v>2</v>
       </c>
-      <c r="BB54" t="inlineStr">
-        <is>
-          <t>COSCO estableció un almacén de más de 20,000 m² en la Zona Libre de Colón en octubre 2020, creando \~100 empleos locales. Fuentes chinas oficiales (People's Daily, China Daily/Qiushi) confirman la operación. Allison indica que no encontró evidencia de la compra ni del monto. El monto de USD 7M es una estimación; no se confirmó si fue compra o alquiler del almacén.</t>
-        </is>
-      </c>
-      <c r="BC54" t="n">
-        <v>1</v>
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>https://xindemarinenews.com/m/view.php?aid=22234</t>
+        </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
+          <t>https://en.people.cn/n3/2024/0819/c90000-20207451.html</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
-        <is>
-          <t>https://xindemarinenews.com/m/view.php?aid=22234</t>
-        </is>
-      </c>
-      <c r="BF54" t="inlineStr">
-        <is>
-          <t>https://en.people.cn/n3/2024/0819/c90000-20207451.html</t>
-        </is>
-      </c>
-      <c r="BG54" t="inlineStr">
         <is>
           <t>https://subsites.chinadaily.com.cn/Qiushi/2024-08/20/c_1014039.htm</t>
         </is>
@@ -7369,7 +7003,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -7407,12 +7041,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Compra de almacén en la zona franca Panapark</t>
+          <t>Compra De Almacén En La Zona Franca Panapark</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Purchase of warehouse in the Panapark free trade zone</t>
+          <t>Purchase Of Warehouse In The Panapark Free Trade Zone</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -7438,20 +7072,20 @@
       <c r="BA55" t="n">
         <v>3</v>
       </c>
-      <c r="BC55" t="n">
-        <v>0</v>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>https://en.coscoshipping.com/col/col6923/art/2025/art_b2dd3208cd3b47d2963d48ec7b07c3be.html</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>https://logistics-manager.com/cosco-shipping-and-xiaomi-deepen-cross-border-collaboration-with-panama-hub/</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
-        <is>
-          <t>https://en.coscoshipping.com/col/col6923/art/2025/art_b2dd3208cd3b47d2963d48ec7b07c3be.html</t>
-        </is>
-      </c>
-      <c r="BF55" t="inlineStr">
-        <is>
-          <t>https://logistics-manager.com/cosco-shipping-and-xiaomi-deepen-cross-border-collaboration-with-panama-hub/</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr">
         <is>
           <t>https://panaparkfreezone.com/en/</t>
         </is>
@@ -7481,7 +7115,7 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -7496,7 +7130,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>CK Hutchison Holdings</t>
+          <t>CK Hutchison (Panama Ports Company)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7550,25 +7184,20 @@
       <c r="BA56" t="n">
         <v>5</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BB56" t="n">
         <v>1</v>
       </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>https://www.csis.org/analysis/chinese-ports-panama-come-under-new-management</t>
+        </is>
+      </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://lexlatin.com/noticias/caso-hutchison-fallo-panama-reglas-project-finance-capital-chino-america-latina</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
-        <is>
-          <t>https://www.csis.org/analysis/chinese-ports-panama-come-under-new-management</t>
-        </is>
-      </c>
-      <c r="BF56" t="inlineStr">
-        <is>
-          <t>https://lexlatin.com/noticias/caso-hutchison-fallo-panama-reglas-project-finance-capital-chino-america-latina</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr">
         <is>
           <t>https://www.infobae.com/panama/2026/01/26/ck-hutchison-evalua-una-venta-fragmentada-de-sus-puertos-incluidos-balboa-y-cristobal-en-panama/?outputType=amp-type</t>
         </is>

--- a/data/sources/countries/panama.xlsx
+++ b/data/sources/countries/panama.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE56"/>
+  <dimension ref="A1:BG56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,20 +684,30 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
@@ -731,10 +740,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G2" t="n">
+        <v>591</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -785,6 +792,9 @@
       <c r="R2" t="n">
         <v>58</v>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -800,23 +810,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
         <v>3</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Huawei estableció su sede regional para América Latina en Panamá en 2011, y en 2015 construyó un Supply Center en la Zona Libre de Colón. Ha creado más de 300 empleos para panameños. Allison confirma que el monto no se puede confirmar. La presencia de Huawei en Panamá está bien documentada pero el monto específico de USD 58M para 'compra de oficina' en 2011 no se verifica en ninguna fuente. | Fuentes adicionales: http://en.yibada.com/articles/70229/20151003/huawei-latin-america-distribution-center-panama.htm</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>http://www.china.org.cn/world/Off_the_Wire/2015-10/02/content_36731925.htm</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>https://americasquarterly.org/article/u-s-pressure-on-huawei-reaches-new-heights-in-panama/</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>https://diazdiaz.com/article/huawei-latam-headquarters-integration-of-technology-and-design</t>
         </is>
@@ -849,10 +893,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G3" t="n">
+        <v>591</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -903,6 +945,9 @@
       <c r="R3" t="n">
         <v>4</v>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -918,22 +963,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
         <v>0</v>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://www.prnewswire.com/news-releases/renesola-establishes-regional-sales-office-in-panama-244849231.html</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>https://www.solarpowerworldonline.com/2014/02/renesola-establishes-regional-sales-office-panama/</t>
         </is>
       </c>
+      <c r="BG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -962,10 +1038,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G4" t="n">
+        <v>591</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1016,6 +1090,9 @@
       <c r="R4" t="n">
         <v>207</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1051,23 +1128,53 @@
           <t>https://www.expedienteabierto.org/wp-content/uploads/2025/04/PANAMA-FACING-THE-CHINESE-CHALLENGE-2.pdf</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Bien documentado: el consorcio CCA-COCIGE (China Construction America + CSCEC + Construcciones Civiles Generales) retomó la construcción del Centro de Convenciones de Amador en febrero 2016 por USD 193M. El monto registrado es USD 207M (posiblemente incluye ajustes). Inaugurado en mayo 2019. Confirmado por CCA, CentralAmericaData y medios internacionales.</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
         <v>0</v>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://www.chinaconstruction.us/project/amador-convention-center/</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>https://centralamericadata.com/en/article/home/Panama_New_Contractor_for_Convention_Center</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>https://www.alwihdainfo.com/Chinese-company-builds-Panama-s-largest-convention-center-enhances-bilateral-ties_a68859.html</t>
         </is>
@@ -1100,10 +1207,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G5" t="n">
+        <v>591</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1154,6 +1259,9 @@
       <c r="R5" t="n">
         <v>165</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1189,23 +1297,53 @@
           <t>https://onepetro.org/ISOPEIOPEC/proceedings-abstract/ISOPE19/ISOPE19/ISOPE-I-19-397/21450?redirectedFrom=PDF</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>5</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Muy bien documentado: CHEC y Jan de Nul ganaron contrato en julio 2017 por USD 165.7M para construir la terminal de cruceros de Fuerte Amador. Ceremonia de inicio el 18 de octubre de 2017. Confirmado por múltiples fuentes especializadas: Maritime Executive, Seatrade Cruise, Chronicle.lu.</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
         <v>0</v>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://maritime-executive.com/article/chec-starts-construction-on-panama-city-cruise-terminal</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>https://chronicle.lu/category/transport-logistics/23694-jan-de-nul-help-construct-amador-cruise-port-in-panama</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>https://www.seatrade-cruise.com/news-headlines/belgium-china-consortium-wins-166m-panama-cruise-terminal-contract</t>
         </is>
@@ -1238,10 +1376,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G6" t="n">
+        <v>591</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1292,6 +1428,9 @@
       <c r="R6" t="n">
         <v>40</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -1307,23 +1446,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Bien documentado: Huawei inauguró centro de distribución latinoamericano en la Zona Libre de Colón el 1 de octubre de 2015, con 10,000 m² de instalaciones. El monto de USD 40M es plausible. Confirmado por China.org.cn y Global Times. El Presidente de Panamá asistió a la inauguración.</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
         <v>0</v>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>http://www.china.org.cn/world/Off_the_Wire/2015-10/02/content_36731925.htm</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/content/945380.shtml</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>https://www.tropicalrealtypanama.com/en/huawei-panama/</t>
         </is>
@@ -1356,10 +1529,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G7" t="n">
+        <v>591</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1410,6 +1581,9 @@
       <c r="R7" t="n">
         <v>259</v>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1425,22 +1599,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
         <v>3</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
         <v>0</v>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>https://thebusinessyear.com/interview/significant-player/</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>https://www.panamaamerica.com.pa/nacion/pagos-empresas-que-construyen-anillos-hidraulicos-estan-al-dia-1236071</t>
         </is>
       </c>
+      <c r="BG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1469,10 +1674,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G8" t="n">
+        <v>591</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1523,6 +1726,9 @@
       <c r="R8" t="n">
         <v>1420</v>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1548,23 +1754,55 @@
           <t>https://revistatongdao.org/index.php/TD/article/download/20/11/119</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Ampliamente documentado: China Daily, Diálogo Américas, CHEC Americas oficial. CCCC/CHEC ganó contrato cuarto puente sobre el Canal de Panamá por $1.4B. Adjudicado jul 2018, orden de proceder dic 2018. Datos coinciden con la base.</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
         <v>0</v>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>https://www.checamerica.com/projects-fourth-bridge/</t>
         </is>
@@ -1597,10 +1835,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G9" t="n">
+        <v>591</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1651,6 +1887,9 @@
       <c r="R9" t="n">
         <v>1420</v>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1676,23 +1915,55 @@
           <t>https://revistatongdao.org/index.php/TD/article/download/20/11/119</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
         <v>5</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Ampliamente documentado: China Daily, Diálogo Américas, CHEC Americas oficial. CCCC/CHEC ganó contrato cuarto puente sobre el Canal de Panamá por $1.4B. Adjudicado jul 2018, orden de proceder dic 2018. Datos coinciden con la base.</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
         <v>0</v>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>https://www.checamerica.com/projects-fourth-bridge/</t>
         </is>
@@ -1725,10 +1996,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G10" t="n">
+        <v>591</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1779,6 +2048,9 @@
       <c r="R10" t="n">
         <v>1420</v>
       </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1804,23 +2076,55 @@
           <t>https://revistatongdao.org/index.php/TD/article/download/20/11/119</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
         <v>5</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Ampliamente documentado: China Daily, Diálogo Américas, CHEC Americas oficial. CCCC/CHEC ganó contrato cuarto puente sobre el Canal de Panamá por $1.4B. Adjudicado jul 2018, orden de proceder dic 2018. Datos coinciden con la base.</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
         <v>0</v>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr">
         <is>
           <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>https://www.checamerica.com/projects-fourth-bridge/</t>
         </is>
@@ -1853,10 +2157,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G11" t="n">
+        <v>591</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1907,6 +2209,9 @@
       <c r="R11" t="n">
         <v>1420</v>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1932,23 +2237,55 @@
           <t>https://revistatongdao.org/index.php/TD/article/download/20/11/119</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
         <v>5</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>Ampliamente documentado: China Daily, Diálogo Américas, CHEC Americas oficial. CCCC/CHEC ganó contrato cuarto puente sobre el Canal de Panamá por $1.4B. Adjudicado jul 2018, orden de proceder dic 2018. Datos coinciden con la base.</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
         <v>0</v>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>https://govt.chinadaily.com.cn/s/201808/06/WS5c08c5be498eefb3fe46e528/cccc-and-chec-to-build-most-sophisticated-bridge-across-panama-canal.html</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>https://dialogo-americas.com/articles/china-to-proceed-with-fourth-bridge-over-panama-canal/</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>https://www.checamerica.com/projects-fourth-bridge/</t>
         </is>
@@ -1981,10 +2318,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G12" t="n">
+        <v>591</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2035,6 +2370,9 @@
       <c r="R12" t="n">
         <v>5</v>
       </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -2050,22 +2388,61 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>Allison dice: 'Eliminar entrada. No existe la compra de oficinas por CCA'. Sin embargo, CCA sí abrió oficina regional en Panamá en abril 2015 (Oceania Business Plaza, Torre 1000, piso 52). La apertura fue un evento con \~300 invitados y fue reportada por múltiples medios. El tema es que fue apertura de oficina (posiblemente arrendada), no compra de USD 5M. La presencia existe pero la descripción como 'compra' es cuestionable.</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>https://www.chinaconstruction.us/</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>https://www.chinaconstruction.us/news/grand-opening-cca-expanded-to-latin-america/</t>
         </is>
       </c>
+      <c r="BG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2094,10 +2471,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G13" t="n">
+        <v>591</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2148,6 +2523,9 @@
       <c r="R13" t="n">
         <v>110</v>
       </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2163,23 +2541,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
         <v>4</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>Contrato EPC confirmado por comunicado oficial de CGGC en MarketScreener y por Seetao, con monto de USD 108M (no 110M). El proyecto Panasolar está documentado de forma independiente. Diferencia menor entre el monto registrado (USD 110M) y el monto contractual (USD 108M).</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
         <v>0</v>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr">
         <is>
           <t>https://www.marketscreener.com/news/latest/CGGC-China-Gezhouba-Signs-An-EPC-Contract-Agreement-for-the-Panamanian-110MW-PV-Project--30671118/</t>
         </is>
       </c>
-      <c r="BD13" t="inlineStr">
+      <c r="BF13" t="inlineStr">
         <is>
           <t>https://www.seetao.com/details/25785.html</t>
         </is>
       </c>
-      <c r="BE13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>https://www.power-technology.com/marketdata/power-plant-profile-panasolar-solar-pv-park-panama/</t>
         </is>
@@ -2212,10 +2624,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G14" t="n">
+        <v>591</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2266,6 +2676,9 @@
       <c r="R14" t="n">
         <v>5</v>
       </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2281,17 +2694,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
         <v>0</v>
       </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="inlineStr">
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Third_Bridge_over_Panama_Canal</t>
         </is>
       </c>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2320,10 +2769,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G15" t="n">
+        <v>591</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2374,6 +2821,9 @@
       <c r="R15" t="n">
         <v>5</v>
       </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2389,17 +2839,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
         <v>0</v>
       </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="inlineStr">
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Third_Bridge_over_Panama_Canal</t>
         </is>
       </c>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2428,10 +2914,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G16" t="n">
+        <v>591</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2482,6 +2966,9 @@
       <c r="R16" t="n">
         <v>5</v>
       </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2497,17 +2984,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="n">
         <v>0</v>
       </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="inlineStr">
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Third_Bridge_over_Panama_Canal</t>
         </is>
       </c>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2536,10 +3059,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G17" t="n">
+        <v>591</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2590,6 +3111,9 @@
       <c r="R17" t="n">
         <v>137</v>
       </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2605,23 +3129,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
         <v>5</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Muy bien documentado: CCA-MCM Consortium inició construcción de Ciudad de Esperanza (City of Hope) en Arraiján el 19 de octubre de 2015 por USD 137M. 2,250 viviendas para 11,250 personas. Confirmado por CCA, Global Construction Review y Global Times. Monto y detalles consistentes con la entrada.</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
         <v>0</v>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr">
         <is>
           <t>https://www.chinaconstruction.us/project/city-of-hope/</t>
         </is>
       </c>
-      <c r="BD17" t="inlineStr">
+      <c r="BF17" t="inlineStr">
         <is>
           <t>https://www.globalconstructionreview.com/chinese-contract8or-beg3ins-work-137m-tow8n-panama/</t>
         </is>
       </c>
-      <c r="BE17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/content/948056.shtml</t>
         </is>
@@ -2654,10 +3212,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G18" t="n">
+        <v>591</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2708,6 +3264,9 @@
       <c r="R18" t="n">
         <v>30</v>
       </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2723,22 +3282,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="n">
         <v>3</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>Confirmado: China Construction America (filial de CSCEC) construyó la estación de buses San Isidro en San Miguelito, primer proyecto de infraestructura de CCA en Panamá. Contrato de \~USD 30M con período de construcción de 540 días. Confirmado por CCA y Chinascope.</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
         <v>0</v>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr">
         <is>
           <t>https://www.chinaconstruction.us/project/san-isidro-bus-station/</t>
         </is>
       </c>
-      <c r="BD18" t="inlineStr">
+      <c r="BF18" t="inlineStr">
         <is>
           <t>https://chinascope.org/archives/16937</t>
         </is>
       </c>
+      <c r="BG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2767,10 +3361,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G19" t="n">
+        <v>591</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2818,6 +3410,10 @@
           <t>PANAMÁ</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -2843,23 +3439,55 @@
           <t>https://revanellis.com/b7ca6ed3-b8d9-4f3f-beb5-7f49d413db4c.pdf.pdf</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
         <v>3</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>ICBC obtuvo licencia bancaria general en Panamá el 12 de junio de 2020, convirtiéndose en el primer banco chino en el país. La licencia fue otorgada por la Superintendencia de Bancos de Panamá. Allison confirma que no puede verificar el monto de USD 3M. El monto estimado parece corresponder a costos de establecimiento de la sucursal. | Fuentes adicionales: https://www.newsroompanama.com/business/giant-china-bank-granted-panama-license</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
         <v>0</v>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr">
         <is>
           <t>https://www.icbc.com.cn/icbc/en/newsupdates/icbc%20news/ICBCPanamaBranchIsGrantedLicense.htm</t>
         </is>
       </c>
-      <c r="BD19" t="inlineStr">
+      <c r="BF19" t="inlineStr">
         <is>
           <t>https://www.panamabanks.info/banks/industrial-and-commercial-bank-of-china-limited</t>
         </is>
       </c>
-      <c r="BE19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>https://www.designbycpu.com/projects/icbcpanama</t>
         </is>
@@ -2892,10 +3520,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G20" t="n">
+        <v>591</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2946,6 +3572,9 @@
       <c r="R20" t="n">
         <v>420</v>
       </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2961,23 +3590,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
         <v>3</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
         <v>0</v>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD20" t="inlineStr">
+      <c r="BF20" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3010,10 +3673,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G21" t="n">
+        <v>591</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3064,6 +3725,9 @@
       <c r="R21" t="n">
         <v>420</v>
       </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3079,23 +3743,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="n">
         <v>3</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
         <v>0</v>
       </c>
-      <c r="BC21" t="inlineStr">
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD21" t="inlineStr">
+      <c r="BF21" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3128,10 +3826,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G22" t="n">
+        <v>591</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3182,6 +3878,9 @@
       <c r="R22" t="n">
         <v>420</v>
       </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3197,23 +3896,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
         <v>3</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
         <v>0</v>
       </c>
-      <c r="BC22" t="inlineStr">
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD22" t="inlineStr">
+      <c r="BF22" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3246,10 +3979,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G23" t="n">
+        <v>591</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3300,6 +4031,9 @@
       <c r="R23" t="n">
         <v>420</v>
       </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3315,23 +4049,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
         <v>3</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
         <v>0</v>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD23" t="inlineStr">
+      <c r="BF23" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3364,10 +4132,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G24" t="n">
+        <v>591</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3418,6 +4184,9 @@
       <c r="R24" t="n">
         <v>420</v>
       </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3433,23 +4202,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
         <v>3</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
         <v>0</v>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD24" t="inlineStr">
+      <c r="BF24" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE24" t="inlineStr">
+      <c r="BG24" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3482,10 +4285,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G25" t="n">
+        <v>591</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3536,6 +4337,9 @@
       <c r="R25" t="n">
         <v>420</v>
       </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3551,23 +4355,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
         <v>3</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
         <v>0</v>
       </c>
-      <c r="BC25" t="inlineStr">
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD25" t="inlineStr">
+      <c r="BF25" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE25" t="inlineStr">
+      <c r="BG25" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3600,10 +4438,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G26" t="n">
+        <v>591</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3654,6 +4490,9 @@
       <c r="R26" t="n">
         <v>420</v>
       </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3669,23 +4508,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
         <v>3</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
         <v>0</v>
       </c>
-      <c r="BC26" t="inlineStr">
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD26" t="inlineStr">
+      <c r="BF26" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE26" t="inlineStr">
+      <c r="BG26" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3718,10 +4591,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G27" t="n">
+        <v>591</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3772,6 +4643,9 @@
       <c r="R27" t="n">
         <v>420</v>
       </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3787,23 +4661,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
         <v>3</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
         <v>0</v>
       </c>
-      <c r="BC27" t="inlineStr">
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD27" t="inlineStr">
+      <c r="BF27" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE27" t="inlineStr">
+      <c r="BG27" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3836,10 +4744,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G28" t="n">
+        <v>591</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3890,6 +4796,9 @@
       <c r="R28" t="n">
         <v>420</v>
       </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3905,23 +4814,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
         <v>3</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
         <v>0</v>
       </c>
-      <c r="BC28" t="inlineStr">
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD28" t="inlineStr">
+      <c r="BF28" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE28" t="inlineStr">
+      <c r="BG28" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -3954,10 +4897,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G29" t="n">
+        <v>591</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4008,6 +4949,9 @@
       <c r="R29" t="n">
         <v>420</v>
       </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4023,23 +4967,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
         <v>3</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
         <v>0</v>
       </c>
-      <c r="BC29" t="inlineStr">
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD29" t="inlineStr">
+      <c r="BF29" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE29" t="inlineStr">
+      <c r="BG29" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4072,10 +5050,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G30" t="n">
+        <v>591</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4126,6 +5102,9 @@
       <c r="R30" t="n">
         <v>420</v>
       </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4141,23 +5120,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
         <v>3</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
         <v>0</v>
       </c>
-      <c r="BC30" t="inlineStr">
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD30" t="inlineStr">
+      <c r="BF30" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE30" t="inlineStr">
+      <c r="BG30" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4190,10 +5203,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G31" t="n">
+        <v>591</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4244,6 +5255,9 @@
       <c r="R31" t="n">
         <v>420</v>
       </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4259,23 +5273,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
         <v>3</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
         <v>0</v>
       </c>
-      <c r="BC31" t="inlineStr">
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD31" t="inlineStr">
+      <c r="BF31" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE31" t="inlineStr">
+      <c r="BG31" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4308,10 +5356,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G32" t="n">
+        <v>591</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4362,6 +5408,9 @@
       <c r="R32" t="n">
         <v>420</v>
       </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4377,23 +5426,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
         <v>3</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
         <v>0</v>
       </c>
-      <c r="BC32" t="inlineStr">
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD32" t="inlineStr">
+      <c r="BF32" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE32" t="inlineStr">
+      <c r="BG32" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4426,10 +5509,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G33" t="n">
+        <v>591</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4480,6 +5561,9 @@
       <c r="R33" t="n">
         <v>420</v>
       </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4495,23 +5579,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
         <v>3</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
         <v>0</v>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD33" t="inlineStr">
+      <c r="BF33" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE33" t="inlineStr">
+      <c r="BG33" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4544,10 +5662,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G34" t="n">
+        <v>591</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4598,6 +5714,9 @@
       <c r="R34" t="n">
         <v>420</v>
       </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4613,23 +5732,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
         <v>3</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC34" t="n">
         <v>0</v>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD34" t="inlineStr">
+      <c r="BF34" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE34" t="inlineStr">
+      <c r="BG34" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4662,10 +5815,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G35" t="n">
+        <v>591</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -4716,6 +5867,9 @@
       <c r="R35" t="n">
         <v>420</v>
       </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4731,23 +5885,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
         <v>3</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC35" t="n">
         <v>0</v>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD35" t="inlineStr">
+      <c r="BF35" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE35" t="inlineStr">
+      <c r="BG35" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4780,10 +5968,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G36" t="n">
+        <v>591</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -4834,6 +6020,9 @@
       <c r="R36" t="n">
         <v>420</v>
       </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4849,23 +6038,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
         <v>3</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC36" t="n">
         <v>0</v>
       </c>
-      <c r="BC36" t="inlineStr">
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD36" t="inlineStr">
+      <c r="BF36" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE36" t="inlineStr">
+      <c r="BG36" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -4898,10 +6121,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G37" t="n">
+        <v>591</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4952,6 +6173,9 @@
       <c r="R37" t="n">
         <v>420</v>
       </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4967,23 +6191,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
         <v>3</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC37" t="n">
         <v>0</v>
       </c>
-      <c r="BC37" t="inlineStr">
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD37" t="inlineStr">
+      <c r="BF37" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE37" t="inlineStr">
+      <c r="BG37" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5016,10 +6274,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G38" t="n">
+        <v>591</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -5070,6 +6326,9 @@
       <c r="R38" t="n">
         <v>420</v>
       </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5085,23 +6344,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
         <v>3</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC38" t="n">
         <v>0</v>
       </c>
-      <c r="BC38" t="inlineStr">
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD38" t="inlineStr">
+      <c r="BF38" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE38" t="inlineStr">
+      <c r="BG38" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5134,10 +6427,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G39" t="n">
+        <v>591</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -5188,6 +6479,9 @@
       <c r="R39" t="n">
         <v>420</v>
       </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5203,23 +6497,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
         <v>3</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC39" t="n">
         <v>0</v>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD39" t="inlineStr">
+      <c r="BF39" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE39" t="inlineStr">
+      <c r="BG39" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5252,10 +6580,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G40" t="n">
+        <v>591</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -5306,6 +6632,9 @@
       <c r="R40" t="n">
         <v>420</v>
       </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5321,23 +6650,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
         <v>3</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC40" t="n">
         <v>0</v>
       </c>
-      <c r="BC40" t="inlineStr">
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD40" t="inlineStr">
+      <c r="BF40" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE40" t="inlineStr">
+      <c r="BG40" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5370,10 +6733,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G41" t="n">
+        <v>591</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -5424,6 +6785,9 @@
       <c r="R41" t="n">
         <v>420</v>
       </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5439,23 +6803,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
         <v>3</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC41" t="n">
         <v>0</v>
       </c>
-      <c r="BC41" t="inlineStr">
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD41" t="inlineStr">
+      <c r="BF41" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE41" t="inlineStr">
+      <c r="BG41" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5488,10 +6886,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G42" t="n">
+        <v>591</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5542,6 +6938,9 @@
       <c r="R42" t="n">
         <v>420</v>
       </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5557,23 +6956,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
         <v>3</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC42" t="n">
         <v>0</v>
       </c>
-      <c r="BC42" t="inlineStr">
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD42" t="inlineStr">
+      <c r="BF42" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE42" t="inlineStr">
+      <c r="BG42" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5606,10 +7039,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G43" t="n">
+        <v>591</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5660,6 +7091,9 @@
       <c r="R43" t="n">
         <v>420</v>
       </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5675,23 +7109,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
         <v>3</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC43" t="n">
         <v>0</v>
       </c>
-      <c r="BC43" t="inlineStr">
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD43" t="inlineStr">
+      <c r="BF43" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE43" t="inlineStr">
+      <c r="BG43" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5724,10 +7192,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G44" t="n">
+        <v>591</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5778,6 +7244,9 @@
       <c r="R44" t="n">
         <v>420</v>
       </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5793,23 +7262,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
         <v>3</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC44" t="n">
         <v>0</v>
       </c>
-      <c r="BC44" t="inlineStr">
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD44" t="inlineStr">
+      <c r="BF44" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE44" t="inlineStr">
+      <c r="BG44" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5842,10 +7345,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G45" t="n">
+        <v>591</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5896,6 +7397,9 @@
       <c r="R45" t="n">
         <v>420</v>
       </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5911,23 +7415,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
         <v>3</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC45" t="n">
         <v>0</v>
       </c>
-      <c r="BC45" t="inlineStr">
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD45" t="inlineStr">
+      <c r="BF45" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE45" t="inlineStr">
+      <c r="BG45" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -5960,10 +7498,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G46" t="n">
+        <v>591</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -6014,6 +7550,9 @@
       <c r="R46" t="n">
         <v>420</v>
       </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6029,23 +7568,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
         <v>3</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC46" t="n">
         <v>0</v>
       </c>
-      <c r="BC46" t="inlineStr">
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD46" t="inlineStr">
+      <c r="BF46" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE46" t="inlineStr">
+      <c r="BG46" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -6078,10 +7651,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G47" t="n">
+        <v>591</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -6132,6 +7703,9 @@
       <c r="R47" t="n">
         <v>420</v>
       </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6147,23 +7721,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="n">
         <v>3</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC47" t="n">
         <v>0</v>
       </c>
-      <c r="BC47" t="inlineStr">
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD47" t="inlineStr">
+      <c r="BF47" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE47" t="inlineStr">
+      <c r="BG47" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -6196,10 +7804,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G48" t="n">
+        <v>591</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -6250,6 +7856,9 @@
       <c r="R48" t="n">
         <v>420</v>
       </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6265,23 +7874,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
       <c r="BA48" t="n">
         <v>3</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>El rol de CRTG en la construccion del tunel submarino de la Linea 3 del Metro de Panama esta bien documentado. El costo total del Tramo Pacifico es aproximadamente USD 420M; CRTG es subcontratista del consorcio coreano HPH, no contratista directo del estado panameno.</t>
+        </is>
+      </c>
+      <c r="BC48" t="n">
         <v>0</v>
       </c>
-      <c r="BC48" t="inlineStr">
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr">
         <is>
           <t>https://www.railway-technology.com/projects/panama-metro-line-3/</t>
         </is>
       </c>
-      <c r="BD48" t="inlineStr">
+      <c r="BF48" t="inlineStr">
         <is>
           <t>https://newsroompanama.com/2023/08/25/chinese-company-will-operate-boring-machine-for-canal-tunnel/</t>
         </is>
       </c>
-      <c r="BE48" t="inlineStr">
+      <c r="BG48" t="inlineStr">
         <is>
           <t>https://ticotimes.net/2025/04/26/new-panama-metro-tunnel-under-the-canal-aims-to-cut-commute-times</t>
         </is>
@@ -6314,10 +7957,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G49" t="n">
+        <v>591</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -6368,6 +8009,9 @@
       <c r="R49" t="n">
         <v>156</v>
       </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6383,23 +8027,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
         <v>4</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>Confirmado por sitio oficial CCA, Global Construction Review, Global Times. China Construction America construyó 'Ciudad de Esperanza' en Vacamonte/Arraiján por $137-156M (2,130-2,250 apartamentos). Adjudicado 2015, entrega programada 2018. Base registra $156M.</t>
+        </is>
+      </c>
+      <c r="BC49" t="n">
         <v>0</v>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr">
         <is>
           <t>https://www.chinaconstruction.us/project/city-of-hope/</t>
         </is>
       </c>
-      <c r="BD49" t="inlineStr">
+      <c r="BF49" t="inlineStr">
         <is>
           <t>https://www.globalconstructionreview.com/chinese-contract8or-beg3ins-work-137m-tow8n-panama/</t>
         </is>
       </c>
-      <c r="BE49" t="inlineStr">
+      <c r="BG49" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/content/948056.shtml</t>
         </is>
@@ -6432,10 +8110,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G50" t="n">
+        <v>591</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6486,6 +8162,9 @@
       <c r="R50" t="n">
         <v>21</v>
       </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6501,22 +8180,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
         <v>2</v>
       </c>
-      <c r="BB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC50" t="inlineStr">
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE50" t="inlineStr">
         <is>
           <t>https://www.aiddata.org/blog/chinas-global-scanner-dissemination</t>
         </is>
       </c>
-      <c r="BD50" t="inlineStr">
+      <c r="BF50" t="inlineStr">
         <is>
           <t>https://www.importgenius.com/panama/importers/nuctech-panama-s-a</t>
         </is>
       </c>
+      <c r="BG50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6545,10 +8259,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G51" t="n">
+        <v>591</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -6596,6 +8308,10 @@
           <t>PANAMÁ</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6611,23 +8327,61 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
         <v>2</v>
       </c>
-      <c r="BB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC51" t="inlineStr">
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>Allison confirma el proyecto y proporciona URL de CCCC en español como evidencia adicional. CCCC Shanghai Dredging tiene presencia registrada en Panamá (Volza, BNamericas). El proyecto de dragado en puerto Balboa en 2024 está confirmado por la propia CCCC. El monto figura como NA, lo cual es consistente con la dificultad de verificar el valor exacto del contrato.</t>
+        </is>
+      </c>
+      <c r="BC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/company-profile/cccc-shanghai-dredging-co-ltd-sdc</t>
         </is>
       </c>
-      <c r="BD51" t="inlineStr">
+      <c r="BF51" t="inlineStr">
         <is>
           <t>https://www.volza.com/company-profile/cccc-shanghai-dredging-company-ltd.-94452941/</t>
         </is>
       </c>
-      <c r="BE51" t="inlineStr">
+      <c r="BG51" t="inlineStr">
         <is>
           <t>https://espanol.ccccltd.cn/xwzx/ztbd/202403/t20240311_213230.html</t>
         </is>
@@ -6660,10 +8414,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G52" t="n">
+        <v>591</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -6711,6 +8463,10 @@
           <t>CHIRIQUÍ</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -6726,22 +8482,61 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
         <v>1</v>
       </c>
-      <c r="BB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>Allison confirma que la operación existe pero no encuentra fecha ni monto. La búsqueda web confirma que Dashang Group (Dalian, China) adquirió Carmen Estate, pero la fecha registrada (2019) no coincide — las fuentes indican que la transferencia ocurrió en 2023. El monto de USD 10M\* no se puede verificar. La operación es real pero año y monto son dudosos.</t>
+        </is>
+      </c>
+      <c r="BC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE52" t="inlineStr">
         <is>
           <t>https://www.roastmasters.com/carmen_copy.html</t>
         </is>
       </c>
-      <c r="BD52" t="inlineStr">
+      <c r="BF52" t="inlineStr">
         <is>
           <t>https://www.chinadaily.com.cn/a/202311/06/WS6548e942a31090682a5ecb99.html</t>
         </is>
       </c>
+      <c r="BG52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6770,10 +8565,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G53" t="n">
+        <v>591</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6824,6 +8617,9 @@
       <c r="R53" t="n">
         <v>10</v>
       </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -6839,23 +8635,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
         <v>3</v>
       </c>
-      <c r="BB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC53" t="inlineStr">
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr">
         <is>
           <t>https://www.cbinsights.com/company/panama-cables-engineering</t>
         </is>
       </c>
-      <c r="BD53" t="inlineStr">
+      <c r="BF53" t="inlineStr">
         <is>
           <t>https://www.hebei-huatong.com/news/the-future-is-coming-from-the-past.html</t>
         </is>
       </c>
-      <c r="BE53" t="inlineStr">
+      <c r="BG53" t="inlineStr">
         <is>
           <t>https://www.hebei-huatong.com/en</t>
         </is>
@@ -6888,10 +8718,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G54" t="n">
+        <v>591</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -6939,6 +8767,10 @@
           <t>PANAMÁ</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -6954,23 +8786,61 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
         <v>2</v>
       </c>
-      <c r="BB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC54" t="inlineStr">
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>COSCO estableció un almacén de más de 20,000 m² en la Zona Libre de Colón en octubre 2020, creando \~100 empleos locales. Fuentes chinas oficiales (People's Daily, China Daily/Qiushi) confirman la operación. Allison indica que no encontró evidencia de la compra ni del monto. El monto de USD 7M es una estimación; no se confirmó si fue compra o alquiler del almacén.</t>
+        </is>
+      </c>
+      <c r="BC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
         <is>
           <t>https://xindemarinenews.com/m/view.php?aid=22234</t>
         </is>
       </c>
-      <c r="BD54" t="inlineStr">
+      <c r="BF54" t="inlineStr">
         <is>
           <t>https://en.people.cn/n3/2024/0819/c90000-20207451.html</t>
         </is>
       </c>
-      <c r="BE54" t="inlineStr">
+      <c r="BG54" t="inlineStr">
         <is>
           <t>https://subsites.chinadaily.com.cn/Qiushi/2024-08/20/c_1014039.htm</t>
         </is>
@@ -7003,10 +8873,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G55" t="n">
+        <v>591</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -7054,6 +8922,10 @@
           <t>PANAMÁ</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -7069,23 +8941,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
         <v>3</v>
       </c>
-      <c r="BB55" t="n">
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="n">
         <v>0</v>
       </c>
-      <c r="BC55" t="inlineStr">
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr">
         <is>
           <t>https://en.coscoshipping.com/col/col6923/art/2025/art_b2dd3208cd3b47d2963d48ec7b07c3be.html</t>
         </is>
       </c>
-      <c r="BD55" t="inlineStr">
+      <c r="BF55" t="inlineStr">
         <is>
           <t>https://logistics-manager.com/cosco-shipping-and-xiaomi-deepen-cross-border-collaboration-with-panama-hub/</t>
         </is>
       </c>
-      <c r="BE55" t="inlineStr">
+      <c r="BG55" t="inlineStr">
         <is>
           <t>https://panaparkfreezone.com/en/</t>
         </is>
@@ -7097,6 +8999,7 @@
           <t>PAN-0001</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>1</v>
       </c>
@@ -7115,10 +9018,8 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="G56" t="n">
+        <v>591</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -7166,6 +9067,10 @@
           <t>COLÓN</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -7181,23 +9086,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
         <v>5</v>
       </c>
-      <c r="BB56" t="n">
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="n">
         <v>1</v>
       </c>
-      <c r="BC56" t="inlineStr">
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr">
         <is>
           <t>https://www.csis.org/analysis/chinese-ports-panama-come-under-new-management</t>
         </is>
       </c>
-      <c r="BD56" t="inlineStr">
+      <c r="BF56" t="inlineStr">
         <is>
           <t>https://lexlatin.com/noticias/caso-hutchison-fallo-panama-reglas-project-finance-capital-chino-america-latina</t>
         </is>
       </c>
-      <c r="BE56" t="inlineStr">
+      <c r="BG56" t="inlineStr">
         <is>
           <t>https://www.infobae.com/panama/2026/01/26/ck-hutchison-evalua-una-venta-fragmentada-de-sus-puertos-incluidos-balboa-y-cristobal-en-panama/?outputType=amp-type</t>
         </is>
